--- a/bi/tkDashboard/库存/库存检查/TK库存检查映射表.xlsx
+++ b/bi/tkDashboard/库存/库存检查/TK库存检查映射表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowHeight="24460" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="源数据路径" sheetId="2" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="110">
   <si>
     <t>表</t>
   </si>
@@ -313,6 +313,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">积加-》销售-》商品管理-》Tiktok自运营-》筛选店铺-》筛选在售
 店铺：
 </t>
@@ -362,6 +369,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">积加-》仓库-》产品库存-》站点产品库存》筛选仓库-》筛选共享
 仓库：
 </t>
@@ -507,6 +521,9 @@
     <t>采购量</t>
   </si>
   <si>
+    <t>☑️</t>
+  </si>
+  <si>
     <t>筛选仓库为美国TK-厦门直邮仓和美国TK-国内厦门仓</t>
   </si>
   <si>
@@ -568,7 +585,7 @@
     <t>库存是否异常</t>
   </si>
   <si>
-    <t>谷仓-3=谷仓-1减谷仓-2</t>
+    <t>谷仓-3=谷仓-1减去谷仓-2</t>
   </si>
   <si>
     <t>谷仓-3</t>
@@ -577,7 +594,7 @@
     <t>库存差异</t>
   </si>
   <si>
-    <t>万邑通USKY3-3=万邑通USKY3-1减万邑通USKY3-2</t>
+    <t>万邑通USKY3-3=万邑通USKY3-1减去万邑通USKY3-2</t>
   </si>
   <si>
     <t>万邑通USKY3-3</t>
@@ -670,6 +687,13 @@
     <t>英国退货仓-1</t>
   </si>
   <si>
+    <t xml:space="preserve">美国站点：
+=谷仓-1+万邑通USKY3-1+万邑通USWC-1+万邑通USWC2-1+国内仓-1+FBT-1（接口能不能抓到？）加FBA(空着)-1
+英国站点：
+=国内仓-1+英国退货仓-1
+</t>
+  </si>
+  <si>
     <t>总库存-1</t>
   </si>
   <si>
@@ -701,9 +725,9 @@
   </si>
   <si>
     <t xml:space="preserve">美国站点：
-=谷仓-2加万邑通USKY3-2加万邑通USWC-2加万邑通USWC2-2加国内仓-2加FBT-2加FBA(空着)-2
+=谷仓-2+万邑通USKY3-2+万邑通USWC-2+万邑通USWC2-2+国内仓-2+FBT-2+FBA(空着)-2
 英国站点：
-=国内仓-2加英国退货仓-2
+=国内仓-2+英国退货仓-2
 </t>
   </si>
   <si>
@@ -1427,7 +1451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1493,15 +1517,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2034,15 +2049,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="10.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="10.1442307692308" customWidth="1"/>
     <col min="2" max="2" width="53.375" customWidth="1"/>
-    <col min="4" max="4" width="35.625" customWidth="1"/>
+    <col min="4" max="4" width="118.394230769231" customWidth="1"/>
     <col min="5" max="5" width="83.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" ht="20.25" spans="1:5">
+    <row r="1" s="18" customFormat="1" ht="23.2" spans="1:5">
       <c r="A1" s="19"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2085,7 +2100,7 @@
         <v>=DISPIMG("ID_16256AFD67E045E8A7AF87229A75DAC8",1)</v>
       </c>
     </row>
-    <row r="4" ht="202.5" spans="1:5">
+    <row r="4" ht="286" spans="1:5">
       <c r="A4" s="20">
         <v>2</v>
       </c>
@@ -2095,7 +2110,7 @@
       <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="str">
@@ -2121,13 +2136,13 @@
       <c r="A6" s="20">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="18" t="s">
         <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="str">
@@ -2137,7 +2152,7 @@
     </row>
     <row r="7" ht="286.7" spans="1:5">
       <c r="A7" s="20"/>
-      <c r="B7" s="23"/>
+      <c r="B7" s="18"/>
       <c r="C7" t="s">
         <v>5</v>
       </c>
@@ -2156,7 +2171,7 @@
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="str">
@@ -2182,17 +2197,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16371"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I16371"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="77.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.025" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.2583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="87.6057692307692" style="1" customWidth="1"/>
+    <col min="3" max="3" width="63.0384615384615" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.2596153846154" style="1" customWidth="1"/>
     <col min="5" max="5" width="47.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.4333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.4326923076923" style="1" customWidth="1"/>
     <col min="9" max="10" width="9" style="1"/>
     <col min="11" max="11" width="12.625" style="1"/>
     <col min="12" max="12" width="9" style="1"/>
@@ -2200,7 +2215,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:8">
+    <row r="1" s="4" customFormat="1" spans="1:9">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2210,7 +2225,7 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" s="4" customFormat="1" spans="1:8">
+    <row r="2" s="4" customFormat="1" spans="1:9">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2220,7 +2235,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" s="4" customFormat="1" spans="1:8">
+    <row r="3" s="4" customFormat="1" ht="17" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -2246,7 +2261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="27" spans="1:8">
+    <row r="4" customFormat="1" ht="34" spans="1:9">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>22</v>
@@ -2265,7 +2280,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" customFormat="1" ht="27" spans="1:8">
+    <row r="5" customFormat="1" ht="34" spans="1:9">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>22</v>
@@ -2284,7 +2299,7 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="27" spans="1:8">
+    <row r="6" customFormat="1" ht="34" spans="1:9">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
         <v>22</v>
@@ -2303,7 +2318,7 @@
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" customFormat="1" ht="27" spans="1:8">
+    <row r="7" customFormat="1" ht="34" spans="1:9">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
         <v>28</v>
@@ -2324,7 +2339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="27" spans="1:8">
+    <row r="8" customFormat="1" ht="34" spans="1:9">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
         <v>22</v>
@@ -2345,7 +2360,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="27" spans="1:8">
+    <row r="9" customFormat="1" ht="34" spans="1:9">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
         <v>22</v>
@@ -2364,7 +2379,7 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" customFormat="1" ht="27" spans="1:8">
+    <row r="10" customFormat="1" ht="17" spans="1:9">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
         <v>22</v>
@@ -2383,7 +2398,7 @@
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" customFormat="1" ht="27" spans="1:8">
+    <row r="11" customFormat="1" ht="17" spans="1:9">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
         <v>36</v>
@@ -2401,10 +2416,14 @@
         <v>37</v>
       </c>
       <c r="G11" s="8"/>
-    </row>
-    <row r="12" ht="27" spans="1:8">
+      <c r="H11"/>
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>36</v>
@@ -2413,19 +2432,23 @@
         <v>7</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="8"/>
-    </row>
-    <row r="13" ht="27" spans="1:8">
+      <c r="H12"/>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="61" customHeight="1" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>36</v>
@@ -2434,19 +2457,23 @@
         <v>7</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="8"/>
-    </row>
-    <row r="14" ht="54" spans="1:8">
+      <c r="H13"/>
+      <c r="I13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="68" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>36</v>
@@ -2455,55 +2482,65 @@
         <v>7</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" s="8"/>
-    </row>
-    <row r="15" ht="27" spans="1:8">
+      <c r="H14"/>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1" spans="1:9">
       <c r="A15" s="7"/>
       <c r="B15" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="8"/>
-    </row>
-    <row r="16" ht="27" spans="1:8">
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="53" customHeight="1" spans="1:9">
       <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="37" customHeight="1" spans="1:9">
       <c r="A17" s="7" t="str">
         <f>"海外在途库存="&amp;F14&amp;"加"&amp;F13</f>
         <v>海外在途库存=三方仓在途量加国内库存</v>
@@ -2515,13 +2552,16 @@
         <v>24</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="8"/>
-    </row>
-    <row r="18" ht="81" spans="1:8">
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" ht="101" spans="1:9">
       <c r="A18" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="7"/>
@@ -2530,14 +2570,17 @@
         <v>24</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="1:9">
       <c r="A19" s="7" t="str">
-        <f>"总在途库存="&amp;F17&amp;"加"&amp;F14&amp;"加"&amp;F15&amp;"加"&amp;F12</f>
-        <v>总在途库存=海外在途库存加三方仓在途量加FBT在途量加交货在途库存</v>
+        <f>"总在途库存="&amp;F17&amp;"+"&amp;F15&amp;"+"&amp;F12</f>
+        <v>总在途库存=海外在途库存+FBT在途量+交货在途库存</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -2546,14 +2589,17 @@
         <v>24</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:9">
       <c r="A20" s="7" t="str">
-        <f>"总可用库存="&amp;F18&amp;"加"&amp;F13</f>
-        <v>总可用库存=海外可用库存加国内库存</v>
+        <f>"总可用库存="&amp;F18&amp;"+"&amp;F13</f>
+        <v>总可用库存=海外可用库存+国内库存</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -2562,14 +2608,17 @@
         <v>24</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" ht="17" spans="1:9">
       <c r="A21" s="7" t="str">
-        <f>"总库存="&amp;F19&amp;"加"&amp;F20</f>
-        <v>总库存=总在途库存加总可用库存</v>
+        <f>"总库存="&amp;F19&amp;"+"&amp;F20</f>
+        <v>总库存=总在途库存+总可用库存</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -2578,13 +2627,16 @@
         <v>24</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="17" spans="1:9">
       <c r="A22" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2593,13 +2645,16 @@
         <v>24</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" ht="17" spans="1:9">
       <c r="A23" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2608,15 +2663,18 @@
         <v>24</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" ht="17" spans="1:9">
       <c r="A24" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2625,13 +2683,16 @@
         <v>24</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="16"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" ht="17" spans="1:9">
       <c r="A25" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2640,13 +2701,16 @@
         <v>24</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G25" s="16"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" ht="17" spans="1:9">
       <c r="A26" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2655,13 +2719,16 @@
         <v>24</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26" s="16"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" ht="17" spans="1:9">
       <c r="A27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2670,13 +2737,16 @@
         <v>24</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="16"/>
-    </row>
-    <row r="28" ht="40.5" spans="1:8">
+      <c r="I27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" ht="51" spans="1:9">
       <c r="A28" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2685,16 +2755,19 @@
         <v>24</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" ht="17" spans="1:9">
       <c r="A29" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2703,13 +2776,13 @@
         <v>24</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G29" s="16"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" ht="17" spans="1:9">
       <c r="A30" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -2718,36 +2791,42 @@
         <v>24</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G30" s="16"/>
-    </row>
-    <row r="31" ht="27" spans="1:8">
+      <c r="I30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" ht="17" spans="1:9">
       <c r="A31" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
-    </row>
-    <row r="32" ht="27" spans="1:8">
+      <c r="I31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" ht="17" spans="1:9">
       <c r="A32" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>36</v>
@@ -2756,99 +2835,114 @@
         <v>7</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" s="16"/>
-    </row>
-    <row r="33" ht="27" spans="1:7">
+      <c r="I32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:9">
       <c r="A33" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" s="16"/>
-    </row>
-    <row r="34" ht="27" spans="1:7">
+      <c r="I33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" ht="17" spans="1:9">
       <c r="A34" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G34" s="16"/>
-    </row>
-    <row r="35" ht="27" spans="1:7">
-      <c r="A35" s="7" t="s">
+      <c r="I34" t="s">
         <v>38</v>
       </c>
+    </row>
+    <row r="35" ht="17" spans="1:9">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="B35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G35" s="16"/>
-    </row>
-    <row r="36" ht="27" spans="1:7">
+      <c r="I35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" ht="17" spans="1:9">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G36" s="16"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="I36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" ht="17" spans="1:9">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -2857,34 +2951,37 @@
         <v>24</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G37" s="16"/>
     </row>
-    <row r="38" ht="27" spans="1:7">
+    <row r="38" ht="17" spans="1:9">
       <c r="A38" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G38" s="16"/>
-    </row>
-    <row r="39" ht="81" spans="1:7">
+      <c r="I38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" ht="101" spans="1:9">
       <c r="A39" s="7" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -2893,11 +2990,14 @@
         <v>24</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G39" s="16"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:7">
+      <c r="I39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" ht="13.5" customHeight="1" spans="1:9">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7" t="s">
@@ -2911,13 +3011,16 @@
         <v>24</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
-    </row>
-    <row r="41" ht="33" spans="1:7">
+      <c r="I40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" ht="28.15" spans="1:9">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7" t="s">
@@ -2931,11 +3034,14 @@
         <v>24</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G41" s="16"/>
-    </row>
-    <row r="42" ht="33" spans="1:7">
+      <c r="I41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" ht="28.15" spans="1:9">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7" t="s">
@@ -2949,11 +3055,14 @@
         <v>24</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G42" s="16"/>
-    </row>
-    <row r="43" ht="33" spans="1:7">
+      <c r="I42" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" ht="28.15" spans="1:9">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7" t="s">
@@ -2967,11 +3076,14 @@
         <v>24</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G43" s="16"/>
-    </row>
-    <row r="44" ht="33" spans="1:7">
+      <c r="I43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" ht="28.15" spans="1:9">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7" t="s">
@@ -2985,11 +3097,14 @@
         <v>24</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G44" s="16"/>
-    </row>
-    <row r="45" ht="44.8" spans="1:7">
+      <c r="I44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" ht="38.45" spans="1:9">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -3001,11 +3116,14 @@
         <v>24</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G45" s="16"/>
-    </row>
-    <row r="46" ht="33" spans="1:7">
+      <c r="I45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" ht="28.15" spans="1:9">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7" t="s">
@@ -3019,11 +3137,14 @@
         <v>24</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G46" s="16"/>
-    </row>
-    <row r="47" ht="33" spans="1:7">
+      <c r="I46" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" ht="28.15" spans="1:9">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
@@ -3037,13 +3158,16 @@
         <v>24</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G47" s="16"/>
-    </row>
-    <row r="48" ht="81" spans="1:7">
+      <c r="I47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" ht="101" spans="1:9">
       <c r="A48" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -3052,9 +3176,12 @@
         <v>24</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G48" s="16"/>
+      <c r="I48" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="49" spans="6:7">
       <c r="F49" s="8"/>
@@ -68356,39 +68483,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="66.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.2583333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.2583333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.2596153846154" customWidth="1"/>
+    <col min="3" max="3" width="20.2596153846154" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" ht="17" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:2">
-      <c r="A3" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="2" ht="17" spans="1:2">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" ht="27" spans="1:2">
+    <row r="3" ht="34" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2">
